--- a/esthetician_forms/016_eyelash_extension_appointment_form--esthetician_forms.xlsx
+++ b/esthetician_forms/016_eyelash_extension_appointment_form--esthetician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -960,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1141,17 +1141,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>sync_app_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>user1</t>
+          <t>100+_apps</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>user1</t>
+          <t>100+ apps</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100+_apps</t>
+          <t>app1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>100+ apps</t>
+          <t>app1</t>
         </is>
       </c>
     </row>
@@ -1180,29 +1180,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>app1</t>
+          <t>app2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>app1</t>
+          <t>app2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sync_app_choices</t>
+          <t>custom_options_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>app2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>app2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1214,29 +1214,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>custom_options_choices</t>
+          <t>embedded_form_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>form1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>form1</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>form1</t>
+          <t>form2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>form1</t>
+          <t>form2</t>
         </is>
       </c>
     </row>
@@ -1265,29 +1265,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>form2</t>
+          <t>form3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>form2</t>
+          <t>form3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>embedded_form_choices</t>
+          <t>easy_share_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form3</t>
+          <t>share1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>form3</t>
+          <t>share1</t>
         </is>
       </c>
     </row>
@@ -1299,29 +1299,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>share1</t>
+          <t>share2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>share1</t>
+          <t>share2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>easy_share_choices</t>
+          <t>easy_embed_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>share2</t>
+          <t>embed1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>share2</t>
+          <t>embed1</t>
         </is>
       </c>
     </row>
@@ -1333,29 +1333,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>embed1</t>
+          <t>embed2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>embed1</t>
+          <t>embed2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>easy_embed_choices</t>
+          <t>customize_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>embed2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>embed2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1367,29 +1367,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>customize_choices</t>
+          <t>share_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>share1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>share1</t>
         </is>
       </c>
     </row>
@@ -1401,27 +1401,10 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>share1</t>
+          <t>share2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
-        <is>
-          <t>share1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>share_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>share2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
         <is>
           <t>share2</t>
         </is>
